--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -35423,7 +35423,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -36961,7 +36961,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -37067,7 +37067,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -37351,10 +37351,14 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>SR-1261</t>
+        </is>
+      </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>08/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -37381,7 +37385,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -37400,10 +37404,14 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>SR-1464</t>
+        </is>
+      </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>08/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -37430,7 +37438,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -37449,10 +37457,14 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>INC-1496</t>
+        </is>
+      </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>08/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -37479,7 +37491,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Jorgenaldo Reis</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -37498,10 +37510,14 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>INC-1554</t>
+        </is>
+      </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>08/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -37528,7 +37544,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -37547,10 +37563,14 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>SR-1159</t>
+        </is>
+      </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>08/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -37577,7 +37597,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -37598,7 +37618,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>INC-1176</t>
+          <t>SR-1709</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -37630,7 +37650,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -37649,14 +37669,10 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>INC-1541</t>
-        </is>
-      </c>
+      <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -37683,7 +37699,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -37702,14 +37718,10 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>SR-1261</t>
-        </is>
-      </c>
+      <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -37789,7 +37801,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -37810,7 +37822,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>SR-1159</t>
+          <t>INC-1519</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -37842,7 +37854,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Jorgenaldo Reis</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -37863,7 +37875,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>INC-1282</t>
+          <t>INC-1535</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -37895,7 +37907,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Jorgenaldo Reis</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -37914,14 +37926,10 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>SR-1607</t>
-        </is>
-      </c>
+      <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -37948,7 +37956,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Jorgenaldo Reis</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -37969,7 +37977,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>SR-1656</t>
+          <t>INC-1282</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -38001,7 +38009,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -38020,14 +38028,10 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>SR-1464</t>
-        </is>
-      </c>
+      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -38054,7 +38058,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -38073,14 +38077,10 @@
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>SR-1694</t>
-        </is>
-      </c>
+      <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>08/2025</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -38107,7 +38107,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SR-1333</t>
+          <t>SR-1366</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -38160,7 +38160,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -38181,7 +38181,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SR-1709</t>
+          <t>SR-1607</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>INC-1584</t>
+          <t>SR-1694</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -38266,7 +38266,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>SR-1366</t>
+          <t>INC-1584</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -38319,7 +38319,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>INC-1496</t>
+          <t>INC-1176</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -38372,7 +38372,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -38393,7 +38393,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>INC-1519</t>
+          <t>INC-1541</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -38446,7 +38446,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>INC-1535</t>
+          <t>SR-1656</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>INC-1554</t>
+          <t>SR-1333</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -11024,7 +11024,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -38616,7 +38616,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -38667,7 +38667,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
@@ -39024,7 +39024,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -39177,7 +39177,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
@@ -39228,7 +39228,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -39687,7 +39687,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
@@ -40197,7 +40197,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -40452,7 +40452,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
@@ -40911,7 +40911,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -43206,7 +43206,7 @@
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
@@ -43512,7 +43512,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
@@ -44430,7 +44430,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -44685,7 +44685,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
@@ -44838,7 +44838,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -44940,7 +44940,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -44991,7 +44991,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -45042,7 +45042,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -10696,7 +10696,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
@@ -38208,7 +38208,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -38747,7 +38747,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -40658,7 +40658,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
@@ -41491,7 +41491,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
@@ -41687,7 +41687,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
@@ -42226,7 +42226,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
@@ -42275,7 +42275,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
@@ -42471,7 +42471,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
@@ -43255,7 +43255,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -43353,7 +43353,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -43451,7 +43451,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K218"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11063,16 +11063,16 @@
         <v>2025</v>
       </c>
       <c r="D216" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -11190,6 +11190,300 @@
         </is>
       </c>
       <c r="K218" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Daniela Klug</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D219" t="n">
+        <v>40</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>2945</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D220" t="n">
+        <v>40</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>3156</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D221" t="n">
+        <v>40</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>3265</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D222" t="n">
+        <v>40</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>329485</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D223" t="n">
+        <v>40</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>340287</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D224" t="n">
+        <v>40</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>344673</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11206,7 +11500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K657"/>
+  <dimension ref="A1:K670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28529,16 +28823,16 @@
         <v>2025</v>
       </c>
       <c r="D354" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -28549,7 +28843,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -36664,27 +36958,27 @@
         <v>2025</v>
       </c>
       <c r="D517" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G517" t="n">
         <v>238</v>
       </c>
       <c r="H517" s="2" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -36860,16 +37154,16 @@
         <v>2025</v>
       </c>
       <c r="D521" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G521" t="n">
@@ -36880,7 +37174,7 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
@@ -36909,16 +37203,16 @@
         <v>2025</v>
       </c>
       <c r="D522" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G522" t="n">
@@ -36929,7 +37223,7 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -36958,16 +37252,16 @@
         <v>2025</v>
       </c>
       <c r="D523" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G523" t="n">
@@ -36978,7 +37272,7 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
@@ -37007,27 +37301,27 @@
         <v>2025</v>
       </c>
       <c r="D524" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G524" t="n">
         <v>1102</v>
       </c>
       <c r="H524" s="2" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -38085,16 +38379,16 @@
         <v>2025</v>
       </c>
       <c r="D546" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G546" t="n">
@@ -38105,7 +38399,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -38281,27 +38575,27 @@
         <v>2025</v>
       </c>
       <c r="D550" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G550" t="n">
         <v>1010</v>
       </c>
       <c r="H550" s="2" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
@@ -39090,7 +39384,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
@@ -39310,27 +39604,27 @@
         <v>2025</v>
       </c>
       <c r="D571" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G571" t="n">
         <v>1045</v>
       </c>
       <c r="H571" s="2" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
@@ -41123,16 +41417,16 @@
         <v>2025</v>
       </c>
       <c r="D608" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G608" t="n">
@@ -41143,7 +41437,7 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
@@ -41540,7 +41834,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
@@ -41834,7 +42128,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
@@ -41907,16 +42201,16 @@
         <v>2025</v>
       </c>
       <c r="D624" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -41927,7 +42221,7 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
@@ -41956,16 +42250,16 @@
         <v>2025</v>
       </c>
       <c r="D625" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G625" t="n">
@@ -41976,7 +42270,7 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
@@ -42005,16 +42299,16 @@
         <v>2025</v>
       </c>
       <c r="D626" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G626" t="n">
@@ -42025,7 +42319,7 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
@@ -42054,16 +42348,16 @@
         <v>2025</v>
       </c>
       <c r="D627" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G627" t="n">
@@ -42074,7 +42368,7 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
@@ -42103,16 +42397,16 @@
         <v>2025</v>
       </c>
       <c r="D628" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G628" t="n">
@@ -42123,7 +42417,7 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
@@ -42495,16 +42789,16 @@
         <v>2025</v>
       </c>
       <c r="D636" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G636" t="n">
@@ -42515,7 +42809,7 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
@@ -42936,16 +43230,16 @@
         <v>2025</v>
       </c>
       <c r="D645" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G645" t="n">
@@ -42956,7 +43250,7 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
@@ -43010,7 +43304,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
@@ -43034,16 +43328,16 @@
         <v>2025</v>
       </c>
       <c r="D647" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G647" t="n">
@@ -43054,7 +43348,7 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
@@ -43083,16 +43377,16 @@
         <v>2025</v>
       </c>
       <c r="D648" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G648" t="n">
@@ -43103,7 +43397,7 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
@@ -43181,16 +43475,16 @@
         <v>2025</v>
       </c>
       <c r="D650" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G650" t="n">
@@ -43201,7 +43495,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -43279,16 +43573,16 @@
         <v>2025</v>
       </c>
       <c r="D652" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -43299,7 +43593,7 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
@@ -43377,16 +43671,16 @@
         <v>2025</v>
       </c>
       <c r="D654" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G654" t="n">
@@ -43397,7 +43691,7 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
@@ -43475,16 +43769,16 @@
         <v>2025</v>
       </c>
       <c r="D656" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G656" t="n">
@@ -43495,7 +43789,7 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
@@ -43524,16 +43818,16 @@
         <v>2025</v>
       </c>
       <c r="D657" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="G657" t="n">
@@ -43544,7 +43838,7 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -43553,6 +43847,643 @@
         </is>
       </c>
       <c r="K657" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D658" t="n">
+        <v>40</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G658" t="n">
+        <v>2845</v>
+      </c>
+      <c r="H658" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D659" t="n">
+        <v>40</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G659" t="n">
+        <v>2925</v>
+      </c>
+      <c r="H659" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D660" t="n">
+        <v>40</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G660" t="n">
+        <v>2996</v>
+      </c>
+      <c r="H660" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D661" t="n">
+        <v>40</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G661" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H661" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D662" t="n">
+        <v>40</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G662" t="n">
+        <v>3037</v>
+      </c>
+      <c r="H662" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D663" t="n">
+        <v>40</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G663" t="n">
+        <v>3038</v>
+      </c>
+      <c r="H663" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D664" t="n">
+        <v>40</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G664" t="n">
+        <v>3110</v>
+      </c>
+      <c r="H664" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D665" t="n">
+        <v>40</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G665" t="n">
+        <v>3191</v>
+      </c>
+      <c r="H665" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Erick da Silva</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D666" t="n">
+        <v>40</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G666" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H666" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D667" t="n">
+        <v>40</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G667" t="n">
+        <v>3201</v>
+      </c>
+      <c r="H667" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D668" t="n">
+        <v>40</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G668" t="n">
+        <v>3203</v>
+      </c>
+      <c r="H668" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D669" t="n">
+        <v>40</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G669" t="n">
+        <v>3250</v>
+      </c>
+      <c r="H669" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D670" t="n">
+        <v>40</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G670" t="n">
+        <v>3264</v>
+      </c>
+      <c r="H670" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -11210,16 +11210,16 @@
         <v>2025</v>
       </c>
       <c r="D219" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -11308,16 +11308,16 @@
         <v>2025</v>
       </c>
       <c r="D221" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -11406,16 +11406,16 @@
         <v>2025</v>
       </c>
       <c r="D223" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -11455,16 +11455,16 @@
         <v>2025</v>
       </c>
       <c r="D224" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -11484,6 +11484,349 @@
         </is>
       </c>
       <c r="K224" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D225" t="n">
+        <v>41</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>3581</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D226" t="n">
+        <v>41</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>3562</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Isabela Borchardt</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D227" t="n">
+        <v>41</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>3410</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Luana Giese</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D228" t="n">
+        <v>41</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>3676</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Luana Giese</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D229" t="n">
+        <v>41</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>3271</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D230" t="n">
+        <v>41</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>3407</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D231" t="n">
+        <v>41</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>3016</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11500,7 +11843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K670"/>
+  <dimension ref="A1:K691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14319,32 +14662,32 @@
         <v>2025</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>323755</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45689</v>
+        <v>45748</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -28823,27 +29166,27 @@
         <v>2025</v>
       </c>
       <c r="D354" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G354" t="n">
         <v>339211</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>45870</v>
+        <v>45931</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -31469,32 +31812,32 @@
         <v>2025</v>
       </c>
       <c r="D408" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G408" t="n">
         <v>342006</v>
       </c>
       <c r="H408" s="2" t="n">
-        <v>45839</v>
+        <v>45901</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -36983,7 +37326,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
@@ -37179,7 +37522,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -37203,16 +37546,16 @@
         <v>2025</v>
       </c>
       <c r="D522" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G522" t="n">
@@ -37223,7 +37566,7 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -37277,7 +37620,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
@@ -37326,7 +37669,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -38379,16 +38722,16 @@
         <v>2025</v>
       </c>
       <c r="D546" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G546" t="n">
@@ -38399,7 +38742,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -38600,7 +38943,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
@@ -39629,7 +39972,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
@@ -41417,16 +41760,16 @@
         <v>2025</v>
       </c>
       <c r="D608" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G608" t="n">
@@ -41437,7 +41780,7 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
@@ -42201,16 +42544,16 @@
         <v>2025</v>
       </c>
       <c r="D624" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -42221,7 +42564,7 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
@@ -42275,7 +42618,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
@@ -42324,7 +42667,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
@@ -42373,7 +42716,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -42422,7 +42765,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
@@ -42814,7 +43157,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
@@ -43255,7 +43598,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -43353,7 +43696,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
@@ -43402,7 +43745,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
@@ -43500,7 +43843,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -43598,7 +43941,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -43671,16 +44014,16 @@
         <v>2025</v>
       </c>
       <c r="D654" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G654" t="n">
@@ -43691,7 +44034,7 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
@@ -43794,7 +44137,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
@@ -43818,16 +44161,16 @@
         <v>2025</v>
       </c>
       <c r="D657" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G657" t="n">
@@ -43838,7 +44181,7 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -43860,7 +44203,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -43880,7 +44223,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>2845</v>
+        <v>2925</v>
       </c>
       <c r="H658" s="2" t="n">
         <v>45901</v>
@@ -43892,7 +44235,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -43909,34 +44252,34 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C659" t="n">
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
-        <v>2925</v>
+        <v>3264</v>
       </c>
       <c r="H659" s="2" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -43958,7 +44301,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -43978,7 +44321,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>2996</v>
+        <v>3200</v>
       </c>
       <c r="H660" s="2" t="n">
         <v>45931</v>
@@ -43990,7 +44333,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -44027,10 +44370,10 @@
         </is>
       </c>
       <c r="G661" t="n">
-        <v>3000</v>
+        <v>2845</v>
       </c>
       <c r="H661" s="2" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="I661" t="inlineStr">
         <is>
@@ -44039,7 +44382,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
@@ -44076,7 +44419,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>3037</v>
+        <v>2996</v>
       </c>
       <c r="H662" s="2" t="n">
         <v>45931</v>
@@ -44088,7 +44431,7 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
@@ -44125,7 +44468,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>3038</v>
+        <v>3000</v>
       </c>
       <c r="H663" s="2" t="n">
         <v>45931</v>
@@ -44137,7 +44480,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -44174,7 +44517,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>3110</v>
+        <v>3037</v>
       </c>
       <c r="H664" s="2" t="n">
         <v>45931</v>
@@ -44186,7 +44529,7 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -44203,7 +44546,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Sostenes Simões</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -44223,7 +44566,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>3191</v>
+        <v>3038</v>
       </c>
       <c r="H665" s="2" t="n">
         <v>45931</v>
@@ -44235,7 +44578,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -44259,27 +44602,27 @@
         <v>2025</v>
       </c>
       <c r="D666" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G666" t="n">
-        <v>3200</v>
+        <v>3110</v>
       </c>
       <c r="H666" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
@@ -44333,7 +44676,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
@@ -44350,7 +44693,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -44370,7 +44713,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>3203</v>
+        <v>3250</v>
       </c>
       <c r="H668" s="2" t="n">
         <v>45931</v>
@@ -44382,7 +44725,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -44399,7 +44742,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -44419,7 +44762,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>3250</v>
+        <v>3203</v>
       </c>
       <c r="H669" s="2" t="n">
         <v>45931</v>
@@ -44431,7 +44774,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -44448,34 +44791,34 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C670" t="n">
         <v>2025</v>
       </c>
       <c r="D670" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="G670" t="n">
-        <v>3264</v>
+        <v>3191</v>
       </c>
       <c r="H670" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
@@ -44484,6 +44827,1035 @@
         </is>
       </c>
       <c r="K670" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D671" t="n">
+        <v>41</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G671" t="n">
+        <v>3060</v>
+      </c>
+      <c r="H671" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D672" t="n">
+        <v>41</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G672" t="n">
+        <v>3224</v>
+      </c>
+      <c r="H672" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D673" t="n">
+        <v>41</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G673" t="n">
+        <v>3364</v>
+      </c>
+      <c r="H673" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D674" t="n">
+        <v>41</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G674" t="n">
+        <v>3424</v>
+      </c>
+      <c r="H674" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D675" t="n">
+        <v>41</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G675" t="n">
+        <v>3425</v>
+      </c>
+      <c r="H675" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D676" t="n">
+        <v>41</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G676" t="n">
+        <v>3516</v>
+      </c>
+      <c r="H676" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D677" t="n">
+        <v>41</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G677" t="n">
+        <v>3620</v>
+      </c>
+      <c r="H677" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D678" t="n">
+        <v>41</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G678" t="n">
+        <v>3359</v>
+      </c>
+      <c r="H678" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D679" t="n">
+        <v>41</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G679" t="n">
+        <v>3476</v>
+      </c>
+      <c r="H679" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D680" t="n">
+        <v>41</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G680" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H680" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Erick da Silva</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D681" t="n">
+        <v>41</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G681" t="n">
+        <v>3396</v>
+      </c>
+      <c r="H681" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Erick da Silva</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D682" t="n">
+        <v>41</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G682" t="n">
+        <v>3526</v>
+      </c>
+      <c r="H682" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D683" t="n">
+        <v>41</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G683" t="n">
+        <v>3305</v>
+      </c>
+      <c r="H683" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D684" t="n">
+        <v>41</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G684" t="n">
+        <v>3418</v>
+      </c>
+      <c r="H684" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D685" t="n">
+        <v>41</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G685" t="n">
+        <v>3693</v>
+      </c>
+      <c r="H685" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D686" t="n">
+        <v>41</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G686" t="n">
+        <v>3381</v>
+      </c>
+      <c r="H686" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Jose Acevedo</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D687" t="n">
+        <v>41</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G687" t="n">
+        <v>3188</v>
+      </c>
+      <c r="H687" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Lourival Moizés</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D688" t="n">
+        <v>41</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G688" t="n">
+        <v>3677</v>
+      </c>
+      <c r="H688" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D689" t="n">
+        <v>41</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G689" t="n">
+        <v>3404</v>
+      </c>
+      <c r="H689" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D690" t="n">
+        <v>41</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G690" t="n">
+        <v>3419</v>
+      </c>
+      <c r="H690" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D691" t="n">
+        <v>41</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="G691" t="n">
+        <v>3703</v>
+      </c>
+      <c r="H691" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -11235,7 +11235,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -44627,7 +44627,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -44823,7 +44823,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
@@ -44970,7 +44970,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
@@ -45166,7 +45166,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
@@ -45313,7 +45313,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
@@ -45362,7 +45362,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -45607,7 +45607,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
@@ -45705,7 +45705,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -11749,16 +11749,16 @@
         <v>2025</v>
       </c>
       <c r="D230" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -11823,10 +11823,402 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Denis Silva</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D232" t="n">
+        <v>42</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>4016</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D233" t="n">
+        <v>42</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>3968</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D234" t="n">
+        <v>42</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>3797</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D235" t="n">
+        <v>42</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>3761</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D236" t="n">
+        <v>42</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>3752</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D237" t="n">
+        <v>42</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>3734</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D238" t="n">
+        <v>42</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>3688</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Higor Cruz</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D239" t="n">
+        <v>42</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>3668</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11843,7 +12235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K691"/>
+  <dimension ref="A1:K705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14687,7 +15079,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -29166,27 +29558,27 @@
         <v>2025</v>
       </c>
       <c r="D354" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G354" t="n">
         <v>339211</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -31837,7 +32229,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -37546,16 +37938,16 @@
         <v>2025</v>
       </c>
       <c r="D522" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G522" t="n">
@@ -37566,7 +37958,7 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -38747,7 +39139,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
@@ -41785,7 +42177,7 @@
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
@@ -42569,7 +42961,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -44039,7 +44431,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -44186,7 +44578,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
@@ -44259,16 +44651,16 @@
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
@@ -44279,7 +44671,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -44847,16 +45239,16 @@
         <v>2025</v>
       </c>
       <c r="D671" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G671" t="n">
@@ -44867,7 +45259,7 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
@@ -44896,16 +45288,16 @@
         <v>2025</v>
       </c>
       <c r="D672" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G672" t="n">
@@ -44916,7 +45308,7 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
@@ -44994,16 +45386,16 @@
         <v>2025</v>
       </c>
       <c r="D674" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G674" t="n">
@@ -45014,7 +45406,7 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -45043,16 +45435,16 @@
         <v>2025</v>
       </c>
       <c r="D675" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G675" t="n">
@@ -45063,7 +45455,7 @@
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
@@ -45092,16 +45484,16 @@
         <v>2025</v>
       </c>
       <c r="D676" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G676" t="n">
@@ -45112,7 +45504,7 @@
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
@@ -45411,7 +45803,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -45435,16 +45827,16 @@
         <v>2025</v>
       </c>
       <c r="D683" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G683" t="n">
@@ -45455,7 +45847,7 @@
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
@@ -45484,16 +45876,16 @@
         <v>2025</v>
       </c>
       <c r="D684" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -45504,7 +45896,7 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
@@ -45624,23 +46016,23 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Jose Acevedo</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C687" t="n">
         <v>2025</v>
       </c>
       <c r="D687" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -45651,7 +46043,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -45729,16 +46121,16 @@
         <v>2025</v>
       </c>
       <c r="D689" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -45749,7 +46141,7 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
@@ -45803,7 +46195,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -45852,10 +46244,696 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D692" t="n">
+        <v>42</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G692" t="n">
+        <v>4261</v>
+      </c>
+      <c r="H692" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr">
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D693" t="n">
+        <v>42</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G693" t="n">
+        <v>4071</v>
+      </c>
+      <c r="H693" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D694" t="n">
+        <v>42</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G694" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H694" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D695" t="n">
+        <v>42</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G695" t="n">
+        <v>3974</v>
+      </c>
+      <c r="H695" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D696" t="n">
+        <v>42</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G696" t="n">
+        <v>3962</v>
+      </c>
+      <c r="H696" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D697" t="n">
+        <v>42</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G697" t="n">
+        <v>3945</v>
+      </c>
+      <c r="H697" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D698" t="n">
+        <v>42</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G698" t="n">
+        <v>3939</v>
+      </c>
+      <c r="H698" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D699" t="n">
+        <v>42</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G699" t="n">
+        <v>3867</v>
+      </c>
+      <c r="H699" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D700" t="n">
+        <v>42</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G700" t="n">
+        <v>3863</v>
+      </c>
+      <c r="H700" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D701" t="n">
+        <v>42</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G701" t="n">
+        <v>3844</v>
+      </c>
+      <c r="H701" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D702" t="n">
+        <v>42</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G702" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H702" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D703" t="n">
+        <v>42</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G703" t="n">
+        <v>3647</v>
+      </c>
+      <c r="H703" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D704" t="n">
+        <v>42</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G704" t="n">
+        <v>3624</v>
+      </c>
+      <c r="H704" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D705" t="n">
+        <v>42</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="G705" t="n">
+        <v>3384</v>
+      </c>
+      <c r="H705" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Higor Cruz</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -36666,7 +36666,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -46261,7 +46261,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -46281,7 +46281,7 @@
         </is>
       </c>
       <c r="G692" t="n">
-        <v>4261</v>
+        <v>4071</v>
       </c>
       <c r="H692" s="2" t="n">
         <v>45931</v>
@@ -46330,7 +46330,7 @@
         </is>
       </c>
       <c r="G693" t="n">
-        <v>4071</v>
+        <v>4008</v>
       </c>
       <c r="H693" s="2" t="n">
         <v>45931</v>
@@ -46379,7 +46379,7 @@
         </is>
       </c>
       <c r="G694" t="n">
-        <v>4008</v>
+        <v>3867</v>
       </c>
       <c r="H694" s="2" t="n">
         <v>45931</v>
@@ -46408,7 +46408,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -46428,7 +46428,7 @@
         </is>
       </c>
       <c r="G695" t="n">
-        <v>3974</v>
+        <v>3863</v>
       </c>
       <c r="H695" s="2" t="n">
         <v>45931</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -46477,7 +46477,7 @@
         </is>
       </c>
       <c r="G696" t="n">
-        <v>3962</v>
+        <v>4261</v>
       </c>
       <c r="H696" s="2" t="n">
         <v>45931</v>
@@ -46506,7 +46506,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -46526,7 +46526,7 @@
         </is>
       </c>
       <c r="G697" t="n">
-        <v>3945</v>
+        <v>3710</v>
       </c>
       <c r="H697" s="2" t="n">
         <v>45931</v>
@@ -46555,7 +46555,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -46575,7 +46575,7 @@
         </is>
       </c>
       <c r="G698" t="n">
-        <v>3939</v>
+        <v>3624</v>
       </c>
       <c r="H698" s="2" t="n">
         <v>45931</v>
@@ -46604,7 +46604,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="G699" t="n">
-        <v>3867</v>
+        <v>3384</v>
       </c>
       <c r="H699" s="2" t="n">
         <v>45931</v>
@@ -46653,7 +46653,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -46673,7 +46673,7 @@
         </is>
       </c>
       <c r="G700" t="n">
-        <v>3863</v>
+        <v>3962</v>
       </c>
       <c r="H700" s="2" t="n">
         <v>45931</v>
@@ -46702,7 +46702,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Sostenes Simões</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -46722,7 +46722,7 @@
         </is>
       </c>
       <c r="G701" t="n">
-        <v>3844</v>
+        <v>3939</v>
       </c>
       <c r="H701" s="2" t="n">
         <v>45931</v>
@@ -46751,7 +46751,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -46771,7 +46771,7 @@
         </is>
       </c>
       <c r="G702" t="n">
-        <v>3710</v>
+        <v>3647</v>
       </c>
       <c r="H702" s="2" t="n">
         <v>45931</v>
@@ -46800,7 +46800,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -46820,7 +46820,7 @@
         </is>
       </c>
       <c r="G703" t="n">
-        <v>3647</v>
+        <v>3945</v>
       </c>
       <c r="H703" s="2" t="n">
         <v>45931</v>
@@ -46849,7 +46849,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -46869,7 +46869,7 @@
         </is>
       </c>
       <c r="G704" t="n">
-        <v>3624</v>
+        <v>3974</v>
       </c>
       <c r="H704" s="2" t="n">
         <v>45931</v>
@@ -46898,7 +46898,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -46918,7 +46918,7 @@
         </is>
       </c>
       <c r="G705" t="n">
-        <v>3384</v>
+        <v>3844</v>
       </c>
       <c r="H705" s="2" t="n">
         <v>45931</v>

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -10615,7 +10615,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Denis Silva</t>
+          <t>Denis da Silva</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Denis Silva</t>
+          <t>Denis da Silva</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Denis Silva</t>
+          <t>Denis da Silva</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Felipe do Nascimento</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C277" t="n">

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K239"/>
+  <dimension ref="A1:K245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -12215,10 +12215,304 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D240" t="n">
+        <v>43</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>4398</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D241" t="n">
+        <v>43</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>4396</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D242" t="n">
+        <v>43</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>4376</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D243" t="n">
+        <v>43</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>4309</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D244" t="n">
+        <v>43</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>4262</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Kleberson Matias</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D245" t="n">
+        <v>43</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>4151</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12235,7 +12529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K705"/>
+  <dimension ref="A1:K727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29583,7 +29877,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -37963,7 +38257,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -44399,23 +44693,23 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C654" t="n">
         <v>2025</v>
       </c>
       <c r="D654" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G654" t="n">
@@ -44426,12 +44720,12 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -44651,16 +44945,16 @@
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
@@ -44671,7 +44965,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -45264,7 +45558,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -45313,7 +45607,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
@@ -45411,7 +45705,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
@@ -45460,7 +45754,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
@@ -45509,7 +45803,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
@@ -45852,7 +46146,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
@@ -45901,7 +46195,7 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -46016,7 +46310,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Jose Acevedo</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -46048,7 +46342,7 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
@@ -46146,7 +46440,7 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
@@ -46293,7 +46587,7 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
@@ -46342,7 +46636,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -46391,7 +46685,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
@@ -46440,7 +46734,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
@@ -46489,7 +46783,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
@@ -46538,7 +46832,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
@@ -46555,23 +46849,23 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C698" t="n">
         <v>2025</v>
       </c>
       <c r="D698" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -46582,7 +46876,7 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
@@ -46636,7 +46930,7 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
@@ -46685,7 +46979,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
@@ -46734,7 +47028,7 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
@@ -46758,16 +47052,16 @@
         <v>2025</v>
       </c>
       <c r="D702" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G702" t="n">
@@ -46778,7 +47072,7 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
@@ -46800,7 +47094,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Jose Acevedo</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -46832,7 +47126,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -46856,16 +47150,16 @@
         <v>2025</v>
       </c>
       <c r="D704" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -46876,7 +47170,7 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
@@ -46905,16 +47199,16 @@
         <v>2025</v>
       </c>
       <c r="D705" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G705" t="n">
@@ -46925,7 +47219,7 @@
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
@@ -46934,6 +47228,1084 @@
         </is>
       </c>
       <c r="K705" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D706" t="n">
+        <v>43</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G706" t="n">
+        <v>4459</v>
+      </c>
+      <c r="H706" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D707" t="n">
+        <v>43</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G707" t="n">
+        <v>4457</v>
+      </c>
+      <c r="H707" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Sostenes Simões</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D708" t="n">
+        <v>43</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G708" t="n">
+        <v>4390</v>
+      </c>
+      <c r="H708" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D709" t="n">
+        <v>43</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G709" t="n">
+        <v>4378</v>
+      </c>
+      <c r="H709" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D710" t="n">
+        <v>43</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G710" t="n">
+        <v>4368</v>
+      </c>
+      <c r="H710" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D711" t="n">
+        <v>43</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G711" t="n">
+        <v>4365</v>
+      </c>
+      <c r="H711" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D712" t="n">
+        <v>43</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G712" t="n">
+        <v>4362</v>
+      </c>
+      <c r="H712" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D713" t="n">
+        <v>43</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G713" t="n">
+        <v>4361</v>
+      </c>
+      <c r="H713" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D714" t="n">
+        <v>43</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G714" t="n">
+        <v>4356</v>
+      </c>
+      <c r="H714" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D715" t="n">
+        <v>43</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G715" t="n">
+        <v>4354</v>
+      </c>
+      <c r="H715" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Matheus Neckel</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D716" t="n">
+        <v>43</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G716" t="n">
+        <v>4339</v>
+      </c>
+      <c r="H716" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D717" t="n">
+        <v>43</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G717" t="n">
+        <v>4335</v>
+      </c>
+      <c r="H717" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D718" t="n">
+        <v>43</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G718" t="n">
+        <v>4326</v>
+      </c>
+      <c r="H718" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D719" t="n">
+        <v>43</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G719" t="n">
+        <v>4319</v>
+      </c>
+      <c r="H719" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D720" t="n">
+        <v>43</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G720" t="n">
+        <v>4281</v>
+      </c>
+      <c r="H720" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D721" t="n">
+        <v>43</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G721" t="n">
+        <v>4242</v>
+      </c>
+      <c r="H721" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D722" t="n">
+        <v>43</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G722" t="n">
+        <v>4224</v>
+      </c>
+      <c r="H722" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D723" t="n">
+        <v>43</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G723" t="n">
+        <v>4202</v>
+      </c>
+      <c r="H723" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D724" t="n">
+        <v>43</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G724" t="n">
+        <v>4134</v>
+      </c>
+      <c r="H724" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D725" t="n">
+        <v>43</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G725" t="n">
+        <v>4099</v>
+      </c>
+      <c r="H725" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D726" t="n">
+        <v>43</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G726" t="n">
+        <v>4063</v>
+      </c>
+      <c r="H726" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D727" t="n">
+        <v>43</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G727" t="n">
+        <v>4062</v>
+      </c>
+      <c r="H727" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/Base/consolidado.xlsx
+++ b/Base/consolidado.xlsx
@@ -12264,7 +12264,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -46881,7 +46881,7 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
@@ -47077,7 +47077,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
@@ -47224,7 +47224,7 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -47241,7 +47241,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -47261,7 +47261,7 @@
         </is>
       </c>
       <c r="G706" t="n">
-        <v>4459</v>
+        <v>4378</v>
       </c>
       <c r="H706" s="2" t="n">
         <v>45931</v>
@@ -47273,7 +47273,7 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
@@ -47290,7 +47290,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -47310,7 +47310,7 @@
         </is>
       </c>
       <c r="G707" t="n">
-        <v>4457</v>
+        <v>4202</v>
       </c>
       <c r="H707" s="2" t="n">
         <v>45931</v>
@@ -47322,7 +47322,7 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
@@ -47339,7 +47339,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Sostenes Simões</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -47359,7 +47359,7 @@
         </is>
       </c>
       <c r="G708" t="n">
-        <v>4390</v>
+        <v>4099</v>
       </c>
       <c r="H708" s="2" t="n">
         <v>45931</v>
@@ -47371,7 +47371,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
@@ -47408,7 +47408,7 @@
         </is>
       </c>
       <c r="G709" t="n">
-        <v>4378</v>
+        <v>4062</v>
       </c>
       <c r="H709" s="2" t="n">
         <v>45931</v>
@@ -47420,7 +47420,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Eduardo da Silva</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -47457,7 +47457,7 @@
         </is>
       </c>
       <c r="G710" t="n">
-        <v>4368</v>
+        <v>4457</v>
       </c>
       <c r="H710" s="2" t="n">
         <v>45931</v>
@@ -47469,7 +47469,7 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
@@ -47486,7 +47486,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -47506,7 +47506,7 @@
         </is>
       </c>
       <c r="G711" t="n">
-        <v>4365</v>
+        <v>4134</v>
       </c>
       <c r="H711" s="2" t="n">
         <v>45931</v>
@@ -47535,7 +47535,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -47555,7 +47555,7 @@
         </is>
       </c>
       <c r="G712" t="n">
-        <v>4362</v>
+        <v>4335</v>
       </c>
       <c r="H712" s="2" t="n">
         <v>45931</v>
@@ -47584,7 +47584,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="G713" t="n">
-        <v>4361</v>
+        <v>4326</v>
       </c>
       <c r="H713" s="2" t="n">
         <v>45931</v>
@@ -47633,7 +47633,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -47653,7 +47653,7 @@
         </is>
       </c>
       <c r="G714" t="n">
-        <v>4356</v>
+        <v>4319</v>
       </c>
       <c r="H714" s="2" t="n">
         <v>45931</v>
@@ -47702,7 +47702,7 @@
         </is>
       </c>
       <c r="G715" t="n">
-        <v>4354</v>
+        <v>4362</v>
       </c>
       <c r="H715" s="2" t="n">
         <v>45931</v>
@@ -47714,7 +47714,7 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
@@ -47731,7 +47731,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Matheus Neckel</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -47751,7 +47751,7 @@
         </is>
       </c>
       <c r="G716" t="n">
-        <v>4339</v>
+        <v>4356</v>
       </c>
       <c r="H716" s="2" t="n">
         <v>45931</v>
@@ -47763,7 +47763,7 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
@@ -47780,7 +47780,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -47800,7 +47800,7 @@
         </is>
       </c>
       <c r="G717" t="n">
-        <v>4335</v>
+        <v>4354</v>
       </c>
       <c r="H717" s="2" t="n">
         <v>45931</v>
@@ -47812,7 +47812,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
@@ -47829,7 +47829,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -47849,7 +47849,7 @@
         </is>
       </c>
       <c r="G718" t="n">
-        <v>4326</v>
+        <v>4281</v>
       </c>
       <c r="H718" s="2" t="n">
         <v>45931</v>
@@ -47861,7 +47861,7 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
@@ -47878,7 +47878,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -47898,7 +47898,7 @@
         </is>
       </c>
       <c r="G719" t="n">
-        <v>4319</v>
+        <v>4365</v>
       </c>
       <c r="H719" s="2" t="n">
         <v>45931</v>
@@ -47927,7 +47927,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -47947,7 +47947,7 @@
         </is>
       </c>
       <c r="G720" t="n">
-        <v>4281</v>
+        <v>4361</v>
       </c>
       <c r="H720" s="2" t="n">
         <v>45931</v>
@@ -47976,7 +47976,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -47996,7 +47996,7 @@
         </is>
       </c>
       <c r="G721" t="n">
-        <v>4242</v>
+        <v>4063</v>
       </c>
       <c r="H721" s="2" t="n">
         <v>45931</v>
@@ -48025,7 +48025,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -48045,7 +48045,7 @@
         </is>
       </c>
       <c r="G722" t="n">
-        <v>4224</v>
+        <v>4459</v>
       </c>
       <c r="H722" s="2" t="n">
         <v>45931</v>
@@ -48057,7 +48057,7 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
@@ -48074,7 +48074,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -48094,7 +48094,7 @@
         </is>
       </c>
       <c r="G723" t="n">
-        <v>4202</v>
+        <v>4368</v>
       </c>
       <c r="H723" s="2" t="n">
         <v>45931</v>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
@@ -48123,7 +48123,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -48143,7 +48143,7 @@
         </is>
       </c>
       <c r="G724" t="n">
-        <v>4134</v>
+        <v>4242</v>
       </c>
       <c r="H724" s="2" t="n">
         <v>45931</v>
@@ -48155,7 +48155,7 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -48192,7 +48192,7 @@
         </is>
       </c>
       <c r="G725" t="n">
-        <v>4099</v>
+        <v>4224</v>
       </c>
       <c r="H725" s="2" t="n">
         <v>45931</v>
@@ -48204,7 +48204,7 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Matheus Neckel</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -48241,7 +48241,7 @@
         </is>
       </c>
       <c r="G726" t="n">
-        <v>4063</v>
+        <v>4339</v>
       </c>
       <c r="H726" s="2" t="n">
         <v>45931</v>
@@ -48253,7 +48253,7 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Sostenes Simões</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -48290,7 +48290,7 @@
         </is>
       </c>
       <c r="G727" t="n">
-        <v>4062</v>
+        <v>4390</v>
       </c>
       <c r="H727" s="2" t="n">
         <v>45931</v>
@@ -48302,7 +48302,7 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
